--- a/inst/testdata/registryid/frs_testpoints_100.xlsx
+++ b/inst/testdata/registryid/frs_testpoints_100.xlsx
@@ -371,7 +371,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>110024338590</v>
+        <v>110044478142</v>
       </c>
     </row>
     <row r="3">
@@ -379,7 +379,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>110001685392</v>
+        <v>110024367308</v>
       </c>
     </row>
     <row r="4">
@@ -387,7 +387,7 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>110070836111</v>
+        <v>110001690590</v>
       </c>
     </row>
     <row r="5">
@@ -395,7 +395,7 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>110004901330</v>
+        <v>110071073502</v>
       </c>
     </row>
     <row r="6">
@@ -403,7 +403,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>110068914198</v>
+        <v>110005193566</v>
       </c>
     </row>
     <row r="7">
@@ -411,7 +411,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>110004017466</v>
+        <v>110068891783</v>
       </c>
     </row>
     <row r="8">
@@ -419,7 +419,7 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>110045578308</v>
+        <v>110004104460</v>
       </c>
     </row>
     <row r="9">
@@ -427,7 +427,7 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>110007446790</v>
+        <v>110045849436</v>
       </c>
     </row>
     <row r="10">
@@ -435,7 +435,7 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>110070404655</v>
+        <v>110007834656</v>
       </c>
     </row>
     <row r="11">
@@ -443,7 +443,7 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>110002815188</v>
+        <v>110070410523</v>
       </c>
     </row>
     <row r="12">
@@ -451,7 +451,7 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>110070514964</v>
+        <v>110002828370</v>
       </c>
     </row>
     <row r="13">
@@ -459,7 +459,7 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>110064786628</v>
+        <v>110070550172</v>
       </c>
     </row>
     <row r="14">
@@ -467,7 +467,7 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>110065408026</v>
+        <v>110064894422</v>
       </c>
     </row>
     <row r="15">
@@ -475,7 +475,7 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>110059841444</v>
+        <v>110065467382</v>
       </c>
     </row>
     <row r="16">
@@ -483,7 +483,7 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>110071467987</v>
+        <v>110060252186</v>
       </c>
     </row>
     <row r="17">
@@ -491,7 +491,7 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>110029392128</v>
+        <v>110072127939</v>
       </c>
     </row>
     <row r="18">
@@ -499,7 +499,7 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>110070229541</v>
+        <v>110071669418</v>
       </c>
     </row>
     <row r="19">
@@ -507,7 +507,7 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>110055717069</v>
+        <v>110029462766</v>
       </c>
     </row>
     <row r="20">
@@ -515,7 +515,7 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>110070055405</v>
+        <v>110071961965</v>
       </c>
     </row>
     <row r="21">
@@ -523,7 +523,7 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>110022505127</v>
+        <v>110070224623</v>
       </c>
     </row>
     <row r="22">
@@ -531,7 +531,7 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>110071198650</v>
+        <v>110055821847</v>
       </c>
     </row>
     <row r="23">
@@ -539,7 +539,7 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>110019306801</v>
+        <v>110070040769</v>
       </c>
     </row>
     <row r="24">
@@ -547,7 +547,7 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>110011461186</v>
+        <v>110072083417</v>
       </c>
     </row>
     <row r="25">
@@ -555,7 +555,7 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>110070020143</v>
+        <v>110022571689</v>
       </c>
     </row>
     <row r="26">
@@ -563,7 +563,7 @@
         <v>25</v>
       </c>
       <c r="B26">
-        <v>110068175432</v>
+        <v>110072113628</v>
       </c>
     </row>
     <row r="27">
@@ -571,7 +571,7 @@
         <v>26</v>
       </c>
       <c r="B27">
-        <v>110015481806</v>
+        <v>110071346716</v>
       </c>
     </row>
     <row r="28">
@@ -579,7 +579,7 @@
         <v>27</v>
       </c>
       <c r="B28">
-        <v>110070581501</v>
+        <v>110019389696</v>
       </c>
     </row>
     <row r="29">
@@ -587,7 +587,7 @@
         <v>28</v>
       </c>
       <c r="B29">
-        <v>110032054112</v>
+        <v>110011649797</v>
       </c>
     </row>
     <row r="30">
@@ -595,7 +595,7 @@
         <v>29</v>
       </c>
       <c r="B30">
-        <v>110041095132</v>
+        <v>110069997907</v>
       </c>
     </row>
     <row r="31">
@@ -603,7 +603,7 @@
         <v>30</v>
       </c>
       <c r="B31">
-        <v>110069998921</v>
+        <v>110068209799</v>
       </c>
     </row>
     <row r="32">
@@ -611,7 +611,7 @@
         <v>31</v>
       </c>
       <c r="B32">
-        <v>110009362732</v>
+        <v>110015562443</v>
       </c>
     </row>
     <row r="33">
@@ -619,7 +619,7 @@
         <v>32</v>
       </c>
       <c r="B33">
-        <v>110033753775</v>
+        <v>110070637122</v>
       </c>
     </row>
     <row r="34">
@@ -627,7 +627,7 @@
         <v>33</v>
       </c>
       <c r="B34">
-        <v>110018157046</v>
+        <v>110032076303</v>
       </c>
     </row>
     <row r="35">
@@ -635,7 +635,7 @@
         <v>34</v>
       </c>
       <c r="B35">
-        <v>110066407285</v>
+        <v>110041384604</v>
       </c>
     </row>
     <row r="36">
@@ -643,7 +643,7 @@
         <v>35</v>
       </c>
       <c r="B36">
-        <v>110018457837</v>
+        <v>110069645566</v>
       </c>
     </row>
     <row r="37">
@@ -651,7 +651,7 @@
         <v>36</v>
       </c>
       <c r="B37">
-        <v>110070588471</v>
+        <v>110009656292</v>
       </c>
     </row>
     <row r="38">
@@ -659,7 +659,7 @@
         <v>37</v>
       </c>
       <c r="B38">
-        <v>110010728178</v>
+        <v>110033806665</v>
       </c>
     </row>
     <row r="39">
@@ -667,7 +667,7 @@
         <v>38</v>
       </c>
       <c r="B39">
-        <v>110039590243</v>
+        <v>110018264402</v>
       </c>
     </row>
     <row r="40">
@@ -675,7 +675,7 @@
         <v>39</v>
       </c>
       <c r="B40">
-        <v>110032890566</v>
+        <v>110066476450</v>
       </c>
     </row>
     <row r="41">
@@ -683,7 +683,7 @@
         <v>40</v>
       </c>
       <c r="B41">
-        <v>110068556486</v>
+        <v>110018586779</v>
       </c>
     </row>
     <row r="42">
@@ -691,7 +691,7 @@
         <v>41</v>
       </c>
       <c r="B42">
-        <v>110066048324</v>
+        <v>110070669298</v>
       </c>
     </row>
     <row r="43">
@@ -699,7 +699,7 @@
         <v>42</v>
       </c>
       <c r="B43">
-        <v>110010697175</v>
+        <v>110010969498</v>
       </c>
     </row>
     <row r="44">
@@ -707,7 +707,7 @@
         <v>43</v>
       </c>
       <c r="B44">
-        <v>110020163375</v>
+        <v>110040125922</v>
       </c>
     </row>
     <row r="45">
@@ -715,7 +715,7 @@
         <v>44</v>
       </c>
       <c r="B45">
-        <v>110071847932</v>
+        <v>110032967136</v>
       </c>
     </row>
     <row r="46">
@@ -723,7 +723,7 @@
         <v>45</v>
       </c>
       <c r="B46">
-        <v>110070699743</v>
+        <v>110068558821</v>
       </c>
     </row>
     <row r="47">
@@ -731,7 +731,7 @@
         <v>46</v>
       </c>
       <c r="B47">
-        <v>110071276108</v>
+        <v>110066115135</v>
       </c>
     </row>
     <row r="48">
@@ -739,7 +739,7 @@
         <v>47</v>
       </c>
       <c r="B48">
-        <v>110032974002</v>
+        <v>110010924250</v>
       </c>
     </row>
     <row r="49">
@@ -747,7 +747,7 @@
         <v>48</v>
       </c>
       <c r="B49">
-        <v>110019164152</v>
+        <v>110020685329</v>
       </c>
     </row>
     <row r="50">
@@ -755,7 +755,7 @@
         <v>49</v>
       </c>
       <c r="B50">
-        <v>110068928174</v>
+        <v>110071916833</v>
       </c>
     </row>
     <row r="51">
@@ -763,7 +763,7 @@
         <v>50</v>
       </c>
       <c r="B51">
-        <v>110070483654</v>
+        <v>110070877530</v>
       </c>
     </row>
     <row r="52">
@@ -771,7 +771,7 @@
         <v>51</v>
       </c>
       <c r="B52">
-        <v>110071202095</v>
+        <v>110071427692</v>
       </c>
     </row>
     <row r="53">
@@ -779,7 +779,7 @@
         <v>52</v>
       </c>
       <c r="B53">
-        <v>110066569895</v>
+        <v>110033110924</v>
       </c>
     </row>
     <row r="54">
@@ -787,7 +787,7 @@
         <v>53</v>
       </c>
       <c r="B54">
-        <v>110070443485</v>
+        <v>110019247885</v>
       </c>
     </row>
     <row r="55">
@@ -795,7 +795,7 @@
         <v>54</v>
       </c>
       <c r="B55">
-        <v>110071335512</v>
+        <v>110068904626</v>
       </c>
     </row>
     <row r="56">
@@ -803,7 +803,7 @@
         <v>55</v>
       </c>
       <c r="B56">
-        <v>110070708117</v>
+        <v>110070514300</v>
       </c>
     </row>
     <row r="57">
@@ -811,7 +811,7 @@
         <v>56</v>
       </c>
       <c r="B57">
-        <v>110071316779</v>
+        <v>110071347440</v>
       </c>
     </row>
     <row r="58">
@@ -819,7 +819,7 @@
         <v>57</v>
       </c>
       <c r="B58">
-        <v>110017186454</v>
+        <v>110066641432</v>
       </c>
     </row>
     <row r="59">
@@ -827,7 +827,7 @@
         <v>58</v>
       </c>
       <c r="B59">
-        <v>110035837921</v>
+        <v>110070454583</v>
       </c>
     </row>
     <row r="60">
@@ -835,7 +835,7 @@
         <v>59</v>
       </c>
       <c r="B60">
-        <v>110003588190</v>
+        <v>110071478903</v>
       </c>
     </row>
     <row r="61">
@@ -843,7 +843,7 @@
         <v>60</v>
       </c>
       <c r="B61">
-        <v>110065780872</v>
+        <v>110070913302</v>
       </c>
     </row>
     <row r="62">
@@ -851,7 +851,7 @@
         <v>61</v>
       </c>
       <c r="B62">
-        <v>110066493654</v>
+        <v>110071470907</v>
       </c>
     </row>
     <row r="63">
@@ -859,7 +859,7 @@
         <v>62</v>
       </c>
       <c r="B63">
-        <v>110071864435</v>
+        <v>110017453325</v>
       </c>
     </row>
     <row r="64">
@@ -867,7 +867,7 @@
         <v>63</v>
       </c>
       <c r="B64">
-        <v>110070101275</v>
+        <v>110036161248</v>
       </c>
     </row>
     <row r="65">
@@ -875,7 +875,7 @@
         <v>64</v>
       </c>
       <c r="B65">
-        <v>110066402119</v>
+        <v>110003652182</v>
       </c>
     </row>
     <row r="66">
@@ -883,7 +883,7 @@
         <v>65</v>
       </c>
       <c r="B66">
-        <v>110044162937</v>
+        <v>110065846954</v>
       </c>
     </row>
     <row r="67">
@@ -891,7 +891,7 @@
         <v>66</v>
       </c>
       <c r="B67">
-        <v>110033121841</v>
+        <v>110066564541</v>
       </c>
     </row>
     <row r="68">
@@ -899,7 +899,7 @@
         <v>67</v>
       </c>
       <c r="B68">
-        <v>110055353362</v>
+        <v>110071924258</v>
       </c>
     </row>
     <row r="69">
@@ -907,7 +907,7 @@
         <v>68</v>
       </c>
       <c r="B69">
-        <v>110025071428</v>
+        <v>110070087734</v>
       </c>
     </row>
     <row r="70">
@@ -915,7 +915,7 @@
         <v>69</v>
       </c>
       <c r="B70">
-        <v>110013822248</v>
+        <v>110066470811</v>
       </c>
     </row>
     <row r="71">
@@ -923,7 +923,7 @@
         <v>70</v>
       </c>
       <c r="B71">
-        <v>110010211314</v>
+        <v>110044346213</v>
       </c>
     </row>
     <row r="72">
@@ -931,7 +931,7 @@
         <v>71</v>
       </c>
       <c r="B72">
-        <v>110039170768</v>
+        <v>110033179922</v>
       </c>
     </row>
     <row r="73">
@@ -939,7 +939,7 @@
         <v>72</v>
       </c>
       <c r="B73">
-        <v>110019075588</v>
+        <v>110055506126</v>
       </c>
     </row>
     <row r="74">
@@ -947,7 +947,7 @@
         <v>73</v>
       </c>
       <c r="B74">
-        <v>110071876375</v>
+        <v>110025100744</v>
       </c>
     </row>
     <row r="75">
@@ -955,7 +955,7 @@
         <v>74</v>
       </c>
       <c r="B75">
-        <v>110070829863</v>
+        <v>110014005469</v>
       </c>
     </row>
     <row r="76">
@@ -963,7 +963,7 @@
         <v>75</v>
       </c>
       <c r="B76">
-        <v>110027700192</v>
+        <v>110010666234</v>
       </c>
     </row>
     <row r="77">
@@ -971,7 +971,7 @@
         <v>76</v>
       </c>
       <c r="B77">
-        <v>110001755477</v>
+        <v>110039302359</v>
       </c>
     </row>
     <row r="78">
@@ -979,7 +979,7 @@
         <v>77</v>
       </c>
       <c r="B78">
-        <v>110071468255</v>
+        <v>110019158285</v>
       </c>
     </row>
     <row r="79">
@@ -987,7 +987,7 @@
         <v>78</v>
       </c>
       <c r="B79">
-        <v>110010739852</v>
+        <v>110071931468</v>
       </c>
     </row>
     <row r="80">
@@ -995,7 +995,7 @@
         <v>79</v>
       </c>
       <c r="B80">
-        <v>110011855634</v>
+        <v>110071065603</v>
       </c>
     </row>
     <row r="81">
@@ -1003,7 +1003,7 @@
         <v>80</v>
       </c>
       <c r="B81">
-        <v>110041304638</v>
+        <v>110027961329</v>
       </c>
     </row>
     <row r="82">
@@ -1011,7 +1011,7 @@
         <v>81</v>
       </c>
       <c r="B82">
-        <v>110067756379</v>
+        <v>110001763930</v>
       </c>
     </row>
     <row r="83">
@@ -1019,7 +1019,7 @@
         <v>82</v>
       </c>
       <c r="B83">
-        <v>110046270771</v>
+        <v>110071669740</v>
       </c>
     </row>
     <row r="84">
@@ -1027,7 +1027,7 @@
         <v>83</v>
       </c>
       <c r="B84">
-        <v>110070274429</v>
+        <v>110011002887</v>
       </c>
     </row>
     <row r="85">
@@ -1035,7 +1035,7 @@
         <v>84</v>
       </c>
       <c r="B85">
-        <v>110033773539</v>
+        <v>110012013579</v>
       </c>
     </row>
     <row r="86">
@@ -1043,7 +1043,7 @@
         <v>85</v>
       </c>
       <c r="B86">
-        <v>110013904864</v>
+        <v>110041445889</v>
       </c>
     </row>
     <row r="87">
@@ -1051,7 +1051,7 @@
         <v>86</v>
       </c>
       <c r="B87">
-        <v>110071145095</v>
+        <v>110067814388</v>
       </c>
     </row>
     <row r="88">
@@ -1059,7 +1059,7 @@
         <v>87</v>
       </c>
       <c r="B88">
-        <v>110070488231</v>
+        <v>110046481669</v>
       </c>
     </row>
     <row r="89">
@@ -1067,7 +1067,7 @@
         <v>88</v>
       </c>
       <c r="B89">
-        <v>110018450399</v>
+        <v>110070274632</v>
       </c>
     </row>
     <row r="90">
@@ -1075,7 +1075,7 @@
         <v>89</v>
       </c>
       <c r="B90">
-        <v>110068803628</v>
+        <v>110033824486</v>
       </c>
     </row>
     <row r="91">
@@ -1083,7 +1083,7 @@
         <v>90</v>
       </c>
       <c r="B91">
-        <v>110014282613</v>
+        <v>110014079219</v>
       </c>
     </row>
     <row r="92">
@@ -1091,7 +1091,7 @@
         <v>91</v>
       </c>
       <c r="B92">
-        <v>110066408177</v>
+        <v>110071295868</v>
       </c>
     </row>
     <row r="93">
@@ -1099,7 +1099,7 @@
         <v>92</v>
       </c>
       <c r="B93">
-        <v>110064335651</v>
+        <v>110070522535</v>
       </c>
     </row>
     <row r="94">
@@ -1107,7 +1107,7 @@
         <v>93</v>
       </c>
       <c r="B94">
-        <v>110065903286</v>
+        <v>110018578323</v>
       </c>
     </row>
     <row r="95">
@@ -1115,7 +1115,7 @@
         <v>94</v>
       </c>
       <c r="B95">
-        <v>110058319065</v>
+        <v>110068788985</v>
       </c>
     </row>
     <row r="96">
@@ -1123,7 +1123,7 @@
         <v>95</v>
       </c>
       <c r="B96">
-        <v>110064555949</v>
+        <v>110014420885</v>
       </c>
     </row>
     <row r="97">
@@ -1131,7 +1131,7 @@
         <v>96</v>
       </c>
       <c r="B97">
-        <v>110018681595</v>
+        <v>110066477529</v>
       </c>
     </row>
     <row r="98">
@@ -1139,7 +1139,7 @@
         <v>97</v>
       </c>
       <c r="B98">
-        <v>110035470291</v>
+        <v>110064432886</v>
       </c>
     </row>
     <row r="99">
@@ -1147,7 +1147,7 @@
         <v>98</v>
       </c>
       <c r="B99">
-        <v>110071397945</v>
+        <v>110065969465</v>
       </c>
     </row>
     <row r="100">
@@ -1155,7 +1155,7 @@
         <v>99</v>
       </c>
       <c r="B100">
-        <v>110066488447</v>
+        <v>110058479766</v>
       </c>
     </row>
     <row r="101">
@@ -1163,7 +1163,7 @@
         <v>100</v>
       </c>
       <c r="B101">
-        <v>110005634858</v>
+        <v>110064640508</v>
       </c>
     </row>
   </sheetData>
